--- a/data/信用债发行汇总_2026-08-25.xlsx
+++ b/data/信用债发行汇总_2026-08-25.xlsx
@@ -1675,7 +1675,9 @@
           <t>2.00 ~ 3.00</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="n">
+        <v>1.75</v>
+      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>齐商银行股份有限公司</t>

--- a/data/信用债发行汇总_2026-08-25.xlsx
+++ b/data/信用债发行汇总_2026-08-25.xlsx
@@ -8994,7 +8994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN24"/>
+  <dimension ref="A1:AN1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9241,4122 +9241,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>08-24 18:00</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>26济南建工MTN001</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>102683324.IB</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>2+N</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>3.00 ~ 4.00</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>济南建工集团有限公司</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>山东省-济南市</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>25济南建工MTN001A</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>1.88Y+2.00Y</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>2.2233</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>国泰海通证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>济南建工集团有限公司2026年度第一期中期票据</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>2028-08-25</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr"/>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr">
-        <is>
-          <t>建筑施工</t>
-        </is>
-      </c>
-      <c r="AF2" s="2" t="inlineStr">
-        <is>
-          <t>房屋建筑</t>
-        </is>
-      </c>
-      <c r="AG2" s="2" t="inlineStr">
-        <is>
-          <t>其他房建</t>
-        </is>
-      </c>
-      <c r="AH2" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK2" s="2" t="inlineStr">
-        <is>
-          <t>永续</t>
-        </is>
-      </c>
-      <c r="AL2" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN2" s="2" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>08-24 19:00</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>26百色02</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>283749.SH</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>2.30 ~ 3.50</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>广西百色试验区发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>广西壮族自治区-百色市</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>26百色01</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>4.80Y</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2.6510</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>2.68</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>天风证券股份有限公司,国海证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>广西百色城市产业发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>广西百色试验区发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>私募</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-26</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr"/>
-      <c r="Z3" s="2" t="inlineStr"/>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AF3" s="2" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AG3" s="2" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AH3" s="2" t="inlineStr">
-        <is>
-          <t>贸易</t>
-        </is>
-      </c>
-      <c r="AI3" s="2" t="inlineStr"/>
-      <c r="AJ3" s="2" t="inlineStr">
-        <is>
-          <t>有担保</t>
-        </is>
-      </c>
-      <c r="AK3" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL3" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>08-24 19:00</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>26沂发02</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>283786.SH</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7Y</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2.50 ~ 3.50</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>新沂经济开发区建设发展有限公司</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>江苏省-徐州市</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>24沂发03</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3.00Y</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1.8412</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>申港证券股份有限公司,国泰海通证券股份有限公司,国金证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>江苏钟吾城乡投资发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>新沂经济开发区建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>私募</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>2033-08-25</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr"/>
-      <c r="Z4" s="2" t="inlineStr"/>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AF4" s="2" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AG4" s="2" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AH4" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI4" s="2" t="inlineStr"/>
-      <c r="AJ4" s="2" t="inlineStr">
-        <is>
-          <t>有担保</t>
-        </is>
-      </c>
-      <c r="AK4" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL4" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM4" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>08-24 19:00</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>26寿光01</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>520439.SZ</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2.30 ~ 3.30</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>寿光市惠农新农村建设投资开发有限公司</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>山东省-潍坊市</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25寿光04</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>3.96Y</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2.2840</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>财达证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>寿光市惠农新农村建设投资开发有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>私募</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-25</t>
-        </is>
-      </c>
-      <c r="Y5" s="2" t="inlineStr"/>
-      <c r="Z5" s="2" t="inlineStr"/>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AD5" s="2" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AF5" s="2" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AG5" s="2" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AH5" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI5" s="2" t="inlineStr"/>
-      <c r="AJ5" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK5" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL5" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>08-24 18:00</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>26太湖新城MTN008</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>102683302.IB</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>10Y</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2.00 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>无锡市太湖新城发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>江苏省-无锡市</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>26太湖新城MTN007</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>9.99Y</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2.3777</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>4-</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>中国民生银行股份有限公司,中国光大银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>无锡市太湖新城发展集团有限公司2026年度第八期中期票据</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X6" s="2" t="inlineStr">
-        <is>
-          <t>2036-08-25</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr"/>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AE6" s="2" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AF6" s="2" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AG6" s="2" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AH6" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI6" s="2" t="inlineStr"/>
-      <c r="AJ6" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK6" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL6" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN6" s="2" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>08-24 18:00</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>26太湖新城MTN009</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>102683316.IB</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10Y</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2.00 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>无锡市太湖新城发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>江苏省-无锡市</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>26太湖新城MTN007</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9.99Y</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2.3777</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4-</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>华夏银行股份有限公司,中国建设银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>无锡市太湖新城发展集团有限公司2026年度第九期中期票据</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X7" s="2" t="inlineStr">
-        <is>
-          <t>2036-08-25</t>
-        </is>
-      </c>
-      <c r="Y7" s="2" t="inlineStr"/>
-      <c r="Z7" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AD7" s="2" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AE7" s="2" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AF7" s="2" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AG7" s="2" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AH7" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI7" s="2" t="inlineStr"/>
-      <c r="AJ7" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK7" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL7" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM7" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN7" s="2" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>08-24 18:00</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>26德阳经开MTN001A</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>102683295.IB</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1.80 ~ 2.80</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>德阳经开区发展(控股)集团有限公司</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>四川省-德阳市</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>25德阳经开MTN001</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>3.52Y</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2.2598</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>长江证券股份有限公司,成都银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>双城(重庆)信用增进股份有限公司</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>德阳经开区发展(控股)集团有限公司2026年度第一期中期票据(品种一)</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X8" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-25</t>
-        </is>
-      </c>
-      <c r="Y8" s="2" t="inlineStr"/>
-      <c r="Z8" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AD8" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AE8" s="2" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AF8" s="2" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AG8" s="2" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AH8" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI8" s="2" t="inlineStr"/>
-      <c r="AJ8" s="2" t="inlineStr">
-        <is>
-          <t>有担保</t>
-        </is>
-      </c>
-      <c r="AK8" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL8" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM8" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>08-24 18:00</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>26德阳经开MTN001B</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>102683296.IB</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1.80 ~ 2.80</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>德阳经开区发展(控股)集团有限公司</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>四川省-德阳市</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>25德阳经开MTN001</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>3.52Y</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>2.2598</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>长江证券股份有限公司,成都银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>重庆三峡融资担保集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>德阳经开区发展(控股)集团有限公司2026年度第一期中期票据(品种二)</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X9" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-25</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="inlineStr"/>
-      <c r="Z9" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AD9" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AE9" s="2" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AF9" s="2" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AG9" s="2" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AH9" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI9" s="2" t="inlineStr"/>
-      <c r="AJ9" s="2" t="inlineStr">
-        <is>
-          <t>有担保</t>
-        </is>
-      </c>
-      <c r="AK9" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL9" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM9" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>08-24 18:00</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>26新疆城建MTN002</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>102690013.IB</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3Y</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1.90 ~ 2.90</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>新疆城建(集团)股份有限公司</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>新疆维吾尔自治区-乌鲁木齐市</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>26新疆城建MTN001</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1.83Y</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2.1651</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>中国国际金融股份有限公司</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>新疆城建(集团)股份有限公司2026年度第二期中期票据</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X10" s="2" t="inlineStr">
-        <is>
-          <t>2029-08-25</t>
-        </is>
-      </c>
-      <c r="Y10" s="2" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AD10" s="2" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="AE10" s="2" t="inlineStr">
-        <is>
-          <t>建筑施工</t>
-        </is>
-      </c>
-      <c r="AF10" s="2" t="inlineStr">
-        <is>
-          <t>综合建筑施工</t>
-        </is>
-      </c>
-      <c r="AG10" s="2" t="inlineStr">
-        <is>
-          <t>综合建筑施工</t>
-        </is>
-      </c>
-      <c r="AH10" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI10" s="2" t="inlineStr"/>
-      <c r="AJ10" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK10" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL10" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM10" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>08-24 18:00</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>26上饶城投PPN003B</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>7Y</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2.00 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>上饶市城市建设投资开发集团有限公司</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>江西省-上饶市</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>24上饶08</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>5.05Y</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2.0540</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>广发证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr"/>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>定向工具(PPN)</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>上饶市城市建设投资开发集团有限公司2026年度第三期定向债务融资工具(品种二)</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>私募</t>
-        </is>
-      </c>
-      <c r="X11" s="2" t="inlineStr">
-        <is>
-          <t>2033-08-25</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="inlineStr"/>
-      <c r="Z11" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AD11" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AE11" s="2" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AF11" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AG11" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AH11" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI11" s="2" t="inlineStr"/>
-      <c r="AJ11" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK11" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL11" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM11" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN11" s="2" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>08-24 19:00</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>26渝旅03</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>283778.SH</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2.00 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>重庆文化旅游集团有限公司</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>26渝旅01</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>4.89Y</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2.2744</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>中信证券股份有限公司,西南证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>华中(武汉)融资担保股份有限公司</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>重庆文化旅游集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>私募</t>
-        </is>
-      </c>
-      <c r="X12" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-26</t>
-        </is>
-      </c>
-      <c r="Y12" s="2" t="inlineStr"/>
-      <c r="Z12" s="2" t="inlineStr"/>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AD12" s="2" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AE12" s="2" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AF12" s="2" t="inlineStr">
-        <is>
-          <t>其他基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AG12" s="2" t="inlineStr">
-        <is>
-          <t>其他基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AH12" s="2" t="inlineStr">
-        <is>
-          <t>旅游综合</t>
-        </is>
-      </c>
-      <c r="AI12" s="2" t="inlineStr"/>
-      <c r="AJ12" s="2" t="inlineStr">
-        <is>
-          <t>有担保</t>
-        </is>
-      </c>
-      <c r="AK12" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL12" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM12" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>08-24 19:00</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>26桂资01</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>283760.SH</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>3Y</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1.80 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>广西资产管理有限公司</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>广西壮族自治区-南宁市</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>25桂金01</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1.76Y</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2.1654</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>华创证券有限责任公司,国海证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>广西资产管理有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>私募</t>
-        </is>
-      </c>
-      <c r="X13" s="2" t="inlineStr">
-        <is>
-          <t>2029-08-26</t>
-        </is>
-      </c>
-      <c r="Y13" s="2" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
-      <c r="Z13" s="2" t="inlineStr"/>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AD13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AE13" s="2" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AF13" s="2" t="inlineStr">
-        <is>
-          <t>资产管理</t>
-        </is>
-      </c>
-      <c r="AG13" s="2" t="inlineStr">
-        <is>
-          <t>资产管理</t>
-        </is>
-      </c>
-      <c r="AH13" s="2" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AI13" s="2" t="inlineStr"/>
-      <c r="AJ13" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK13" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL13" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM13" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>08-24 18:00</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>26临沂投资PPN001</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1.80 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>临沂投资发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>山东省-临沂市</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>24临沂投资PPN002</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2.91Y</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2.0932</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>长城证券股份有限公司,青岛银行股份有限公司,申万宏源证券有限公司,中信证券股份有限公司,东方证券股份有限公司,广发证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr"/>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>定向工具(PPN)</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>临沂投资发展集团有限公司2026年度第一期定向债务融资工具</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>私募</t>
-        </is>
-      </c>
-      <c r="X14" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-25</t>
-        </is>
-      </c>
-      <c r="Y14" s="2" t="inlineStr"/>
-      <c r="Z14" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AD14" s="2" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AE14" s="2" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AF14" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AG14" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AH14" s="2" t="inlineStr">
-        <is>
-          <t>钢铁</t>
-        </is>
-      </c>
-      <c r="AI14" s="2" t="inlineStr"/>
-      <c r="AJ14" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK14" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL14" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM14" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>08-24 18:00</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>26济南高新MTN007B</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>102683304.IB</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>5+N</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>济南高新控股集团有限公司</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>山东省-济南市</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>26济南高新MTN001B</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>4.44Y+N</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>2.0834</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>5+</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>中信建投证券股份有限公司,平安银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr"/>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>济南高新控股集团有限公司2026年度第七期中期票据(品种二)</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X15" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-25</t>
-        </is>
-      </c>
-      <c r="Y15" s="2" t="inlineStr"/>
-      <c r="Z15" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AD15" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AE15" s="2" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AF15" s="2" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AG15" s="2" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AH15" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI15" s="2" t="inlineStr"/>
-      <c r="AJ15" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK15" s="2" t="inlineStr">
-        <is>
-          <t>永续</t>
-        </is>
-      </c>
-      <c r="AL15" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM15" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>08-24 18:00</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>26中铁十一MTN002B</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>102683318.IB</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>5+N</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>中铁十一局集团有限公司</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>湖北省-武汉市</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>26中铁十一MTN001B</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>4.97Y+N</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2.1286</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5+</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2.13</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>国泰海通证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>国有企业</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>中铁十一局集团有限公司2026年度第二期中期票据(品种二)</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X16" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-25</t>
-        </is>
-      </c>
-      <c r="Y16" s="2" t="inlineStr"/>
-      <c r="Z16" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AD16" s="2" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="AE16" s="2" t="inlineStr">
-        <is>
-          <t>建筑施工</t>
-        </is>
-      </c>
-      <c r="AF16" s="2" t="inlineStr">
-        <is>
-          <t>专业工程</t>
-        </is>
-      </c>
-      <c r="AG16" s="2" t="inlineStr">
-        <is>
-          <t>市政路桥</t>
-        </is>
-      </c>
-      <c r="AH16" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI16" s="2" t="inlineStr"/>
-      <c r="AJ16" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK16" s="2" t="inlineStr">
-        <is>
-          <t>永续</t>
-        </is>
-      </c>
-      <c r="AL16" s="2" t="inlineStr">
-        <is>
-          <t>次级债权</t>
-        </is>
-      </c>
-      <c r="AM16" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN16" s="2" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>08-24 19:00</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>26安租Y6</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>245894.SH</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>3+N</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2.00 ~ 2.80</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>平安国际融资租赁有限公司</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>上海市</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>26安租Y4</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1.64Y+N</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1.9643</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>4-</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>平安证券股份有限公司,中信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr"/>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>民营企业</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>平安国际融资租赁有限公司2026年面向专业投资者公开发行可续期公司债券(第三期)</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X17" s="2" t="inlineStr">
-        <is>
-          <t>2029-08-26</t>
-        </is>
-      </c>
-      <c r="Y17" s="2" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
-      <c r="Z17" s="2" t="inlineStr"/>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AD17" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AE17" s="2" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AF17" s="2" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="AG17" s="2" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="AH17" s="2" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AI17" s="2" t="inlineStr"/>
-      <c r="AJ17" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK17" s="2" t="inlineStr">
-        <is>
-          <t>永续</t>
-        </is>
-      </c>
-      <c r="AL17" s="2" t="inlineStr">
-        <is>
-          <t>次级债权</t>
-        </is>
-      </c>
-      <c r="AM17" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>08-24 18:00</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>26上饶城投PPN003A</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>上饶市城市建设投资开发集团有限公司</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>江西省-上饶市</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>24上饶07</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>5.00Y</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>2.0440</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>广发证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr"/>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>定向工具(PPN)</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>上饶市城市建设投资开发集团有限公司2026年度第三期定向债务融资工具(品种一)</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>私募</t>
-        </is>
-      </c>
-      <c r="X18" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-25</t>
-        </is>
-      </c>
-      <c r="Y18" s="2" t="inlineStr"/>
-      <c r="Z18" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AD18" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AE18" s="2" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AF18" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AG18" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AH18" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI18" s="2" t="inlineStr"/>
-      <c r="AJ18" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK18" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL18" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM18" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN18" s="2" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>08-24 18:00</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>26荆门城建MTN002</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>102683301.IB</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>5+5</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1.80 ~ 2.80</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>湖北荆门城建集团有限公司</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>湖北省-荆门市</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>25荆门城建MTN005</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>3.82Y</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2.0171</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>平安证券股份有限公司,国泰海通证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr"/>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>湖北荆门城建集团有限公司2026年度第二期中期票据</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X19" s="2" t="inlineStr">
-        <is>
-          <t>2036-08-25</t>
-        </is>
-      </c>
-      <c r="Y19" s="2" t="inlineStr"/>
-      <c r="Z19" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AD19" s="2" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AE19" s="2" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AF19" s="2" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AG19" s="2" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AH19" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI19" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-25</t>
-        </is>
-      </c>
-      <c r="AJ19" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK19" s="2" t="inlineStr">
-        <is>
-          <t>含权</t>
-        </is>
-      </c>
-      <c r="AL19" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM19" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN19" s="2" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>08-24 19:00</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>26沂发01</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>283785.SH</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2.00 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>新沂经济开发区建设发展有限公司</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>江苏省-徐州市</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>24沂发03</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>3.00Y</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1.8412</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>申港证券股份有限公司,国泰海通证券股份有限公司,国金证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>江苏钟吾城乡投资发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>新沂经济开发区建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>私募</t>
-        </is>
-      </c>
-      <c r="X20" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-25</t>
-        </is>
-      </c>
-      <c r="Y20" s="2" t="inlineStr"/>
-      <c r="Z20" s="2" t="inlineStr"/>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AC20" s="2" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AD20" s="2" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AE20" s="2" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AF20" s="2" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AG20" s="2" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AH20" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI20" s="2" t="inlineStr"/>
-      <c r="AJ20" s="2" t="inlineStr">
-        <is>
-          <t>有担保</t>
-        </is>
-      </c>
-      <c r="AK20" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL20" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM20" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>08-24 19:00</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>26东财R2</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>283748.SH</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>1.80 ~ 2.80</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>东营市财金投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>山东省-东营市</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>25东财01</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>3.50Y</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>1.9014</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>浙商证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr"/>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>东营市财金投资集团有限公司2026年面向专业投资者非公开发行一带一路公司债券(第一期)(品种二)</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>私募</t>
-        </is>
-      </c>
-      <c r="X21" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-26</t>
-        </is>
-      </c>
-      <c r="Y21" s="2" t="inlineStr"/>
-      <c r="Z21" s="2" t="inlineStr"/>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AD21" s="2" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AE21" s="2" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AF21" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AG21" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AH21" s="2" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AI21" s="2" t="inlineStr"/>
-      <c r="AJ21" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK21" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL21" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM21" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>08-24 18:00</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>26西安经发MTN001</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>102683306.IB</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2.00 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>西安经发控股(集团)有限责任公司</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>陕西省-西安市</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>24西安经发MTN001</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>248D</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1.6234</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr"/>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>国金证券股份有限公司,招商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr"/>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>西安经发控股(集团)有限责任公司2026年度第一期中期票据</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X22" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-25</t>
-        </is>
-      </c>
-      <c r="Y22" s="2" t="inlineStr"/>
-      <c r="Z22" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AD22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AE22" s="2" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AF22" s="2" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AG22" s="2" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AH22" s="2" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AI22" s="2" t="inlineStr"/>
-      <c r="AJ22" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK22" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL22" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM22" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>08-24 19:00</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>26青城11</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>283744.SH</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>5+3+2</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>青岛城市建设投资(集团)有限责任公司</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>山东省-青岛市</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>26青城09</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>4.65Y+5.00Y</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>1.9742</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr"/>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>中信证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,招商证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr"/>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>青岛城市建设投资(集团)有限责任公司2026年面向专业投资者非公开发行公司债券(第六期)(品种一)</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>私募</t>
-        </is>
-      </c>
-      <c r="X23" s="2" t="inlineStr">
-        <is>
-          <t>2036-08-26</t>
-        </is>
-      </c>
-      <c r="Y23" s="2" t="inlineStr"/>
-      <c r="Z23" s="2" t="inlineStr"/>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AD23" s="2" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AE23" s="2" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AF23" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AG23" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AH23" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI23" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-26</t>
-        </is>
-      </c>
-      <c r="AJ23" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK23" s="2" t="inlineStr">
-        <is>
-          <t>含权</t>
-        </is>
-      </c>
-      <c r="AL23" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM23" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>08-24 19:00</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>26郑安02</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>283741.SH</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>郑州城发安居科技有限公司</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>河南省-郑州市</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>26郑安01</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>4.78Y</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>2.0141</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>5+</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr"/>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>华泰联合证券有限责任公司,平安证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr"/>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>郑州城发安居科技有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>私募</t>
-        </is>
-      </c>
-      <c r="X24" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-26</t>
-        </is>
-      </c>
-      <c r="Y24" s="2" t="inlineStr"/>
-      <c r="Z24" s="2" t="inlineStr"/>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AD24" s="2" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AE24" s="2" t="inlineStr">
-        <is>
-          <t>房地产</t>
-        </is>
-      </c>
-      <c r="AF24" s="2" t="inlineStr">
-        <is>
-          <t>综合地产</t>
-        </is>
-      </c>
-      <c r="AG24" s="2" t="inlineStr">
-        <is>
-          <t>综合地产</t>
-        </is>
-      </c>
-      <c r="AH24" s="2" t="inlineStr">
-        <is>
-          <t>计算机应用</t>
-        </is>
-      </c>
-      <c r="AI24" s="2" t="inlineStr"/>
-      <c r="AJ24" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK24" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL24" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM24" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN24" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
